--- a/artfynd/A 27759-2026 artfynd.xlsx
+++ b/artfynd/A 27759-2026 artfynd.xlsx
@@ -1370,7 +1370,7 @@
         <v>74112706</v>
       </c>
       <c r="B8" t="n">
-        <v>96665</v>
+        <v>96668</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 27759-2026 artfynd.xlsx
+++ b/artfynd/A 27759-2026 artfynd.xlsx
@@ -1370,7 +1370,7 @@
         <v>74112706</v>
       </c>
       <c r="B8" t="n">
-        <v>96668</v>
+        <v>96669</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 27759-2026 artfynd.xlsx
+++ b/artfynd/A 27759-2026 artfynd.xlsx
@@ -1370,7 +1370,7 @@
         <v>74112706</v>
       </c>
       <c r="B8" t="n">
-        <v>96669</v>
+        <v>96674</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 27759-2026 artfynd.xlsx
+++ b/artfynd/A 27759-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ97"/>
+  <dimension ref="A1:AZ114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1917,10 +1917,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>74112505</v>
+        <v>137124402</v>
       </c>
       <c r="B13" t="n">
-        <v>89885</v>
+        <v>87492</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1928,35 +1928,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5565</v>
+        <v>3674</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pluteus cyanopus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bäl-Gane, Gtl</t>
+          <t>Bål Gute, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>719347</v>
+        <v>719397</v>
       </c>
       <c r="R13" t="n">
-        <v>6395072</v>
+        <v>6394987</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1980,12 +1982,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2018-09-26</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2018-10-27</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1994,59 +2006,33 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Blandsumpskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>ved av ask</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior # ved av ask</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/74112505</t>
+          <t>https://artportalen.se/Sighting/137124402</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119645925</v>
+        <v>137124403</v>
       </c>
       <c r="B14" t="n">
-        <v>57247</v>
+        <v>87492</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2054,45 +2040,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100038</v>
+        <v>3674</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Bål Gute, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>719367</v>
+        <v>719404</v>
       </c>
       <c r="R14" t="n">
-        <v>6395063</v>
+        <v>6394824</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2116,12 +2094,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2136,27 +2124,27 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119645925</t>
+          <t>https://artportalen.se/Sighting/137124403</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135025195</v>
+        <v>137124405</v>
       </c>
       <c r="B15" t="n">
-        <v>57977</v>
+        <v>87492</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2164,46 +2152,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>3674</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bäl Gute 1:46 A 27759-2026., Gtl</t>
+          <t>Bål Gute, Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>719388</v>
+        <v>719462</v>
       </c>
       <c r="R15" t="n">
-        <v>6395017</v>
+        <v>6394769</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2227,12 +2206,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,36 +2232,31 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Ängsbarrskog.</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025195</t>
+          <t>https://artportalen.se/Sighting/137124405</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135025196</v>
+        <v>137124410</v>
       </c>
       <c r="B16" t="n">
-        <v>57977</v>
+        <v>87492</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2280,42 +2264,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>3674</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bäl Gute 1:46 A 27759-2026., Gtl</t>
+          <t>Bål Gute, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>719368</v>
+        <v>719496</v>
       </c>
       <c r="R16" t="n">
-        <v>6394966</v>
+        <v>6394908</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2339,17 +2318,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Födosök i död gran.</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2360,36 +2344,31 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Ängsbarrskog.</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025196</t>
+          <t>https://artportalen.se/Sighting/137124410</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119645924</v>
+        <v>137124411</v>
       </c>
       <c r="B17" t="n">
-        <v>58085</v>
+        <v>87492</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2397,37 +2376,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>205976</v>
+        <v>3674</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Bål Gute, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>719342</v>
+        <v>719488</v>
       </c>
       <c r="R17" t="n">
-        <v>6395013</v>
+        <v>6394959</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2451,12 +2430,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2471,27 +2460,27 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119645924</t>
+          <t>https://artportalen.se/Sighting/137124411</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135025043</v>
+        <v>137124389</v>
       </c>
       <c r="B18" t="n">
-        <v>111342</v>
+        <v>93088</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2499,34 +2488,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219677</v>
+        <v>4769</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bäl Gute 1:46 A 27759-2026., Gtl</t>
+          <t>Bäl, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>719351</v>
+        <v>719272</v>
       </c>
       <c r="R18" t="n">
-        <v>6394940</v>
+        <v>6394853</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2553,17 +2542,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Flera grova tallar mot NO.</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2574,36 +2568,31 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Ängsbarrskog, träd på socklar.</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025043</t>
+          <t>https://artportalen.se/Sighting/137124389</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135025047</v>
+        <v>137124397</v>
       </c>
       <c r="B19" t="n">
-        <v>111342</v>
+        <v>93088</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2611,37 +2600,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219677</v>
+        <v>4769</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bäl Gute 1:46 A 27759-2026., Gtl</t>
+          <t>Bål Gute, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>719372</v>
+        <v>719356</v>
       </c>
       <c r="R19" t="n">
-        <v>6394909</v>
+        <v>6395104</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2665,17 +2654,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>I döende björk.</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2686,36 +2680,31 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Ängsbarrskog, träd på socklar.</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025047</t>
+          <t>https://artportalen.se/Sighting/137124397</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135025061</v>
+        <v>74112505</v>
       </c>
       <c r="B20" t="n">
-        <v>111342</v>
+        <v>89885</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2723,46 +2712,35 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219677</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Murgröna</t>
-        </is>
+        <v>5565</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Pluteus cyanopus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bäl Gute 1:46 A 27759-2026., Gtl</t>
+          <t>Bäl-Gane, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>719423</v>
+        <v>719347</v>
       </c>
       <c r="R20" t="n">
-        <v>6394896</v>
+        <v>6395072</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2786,17 +2764,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2018-09-26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>I träd med Snitsel hänsyn mot N.</t>
+          <t>2018-10-27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2805,73 +2778,94 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Ängsbarrskog, träd på socklar.</t>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>ved av ask</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior # ved av ask</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025061</t>
+          <t>https://artportalen.se/Sighting/74112505</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135025070</v>
+        <v>137124390</v>
       </c>
       <c r="B21" t="n">
-        <v>111342</v>
+        <v>93452</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219677</v>
+        <v>5964</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bäl Gute 1:46 A 27759-2026., Gtl</t>
+          <t>Bäl, Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>719318</v>
+        <v>719259</v>
       </c>
       <c r="R21" t="n">
-        <v>6394792</v>
+        <v>6394844</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2898,17 +2892,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Dike SO. I träd.</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2919,74 +2918,69 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Ängsbarrskog, träd på socklar. Närmast sumpskog.</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025070</t>
+          <t>https://artportalen.se/Sighting/137124390</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135025079</v>
+        <v>137124399</v>
       </c>
       <c r="B22" t="n">
-        <v>111342</v>
+        <v>75566</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219677</v>
+        <v>6426</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bäl Gute 1:46 A 27759-2026., Gtl</t>
+          <t>Bål Gute, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>719282</v>
+        <v>719421</v>
       </c>
       <c r="R22" t="n">
-        <v>6394872</v>
+        <v>6395031</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3010,17 +3004,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>I träd.</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3031,83 +3030,77 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Ängsbarrskog.</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025079</t>
+          <t>https://artportalen.se/Sighting/137124399</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135025001</v>
+        <v>119645925</v>
       </c>
       <c r="B23" t="n">
-        <v>111556</v>
+        <v>57247</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219711</v>
+        <v>100038</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bäl Gute 1:46 A 27759-2026., Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>719343</v>
+        <v>719367</v>
       </c>
       <c r="R23" t="n">
-        <v>6395110</v>
+        <v>6395063</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3131,12 +3124,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3147,36 +3140,31 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Ängsbarrskog, träd på socklar.</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025001</t>
+          <t>https://artportalen.se/Sighting/119645925</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135025002</v>
+        <v>135025195</v>
       </c>
       <c r="B24" t="n">
-        <v>99247</v>
+        <v>57977</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3184,31 +3172,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3217,13 +3205,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>719343</v>
+        <v>719388</v>
       </c>
       <c r="R24" t="n">
-        <v>6395110</v>
+        <v>6395017</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3266,7 +3254,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Ängsbarrskog, träd på socklar.</t>
+          <t>Ängsbarrskog.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3283,16 +3271,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025002</t>
+          <t>https://artportalen.se/Sighting/135025195</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135025009</v>
+        <v>135025196</v>
       </c>
       <c r="B25" t="n">
-        <v>99247</v>
+        <v>57977</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3300,31 +3288,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3333,10 +3317,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>719338</v>
+        <v>719368</v>
       </c>
       <c r="R25" t="n">
-        <v>6395097</v>
+        <v>6394966</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3371,6 +3355,11 @@
           <t>2026-06-30</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Födosök i död gran.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3382,7 +3371,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Ängsbarrskog, träd på socklar.</t>
+          <t>Ängsbarrskog.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3399,16 +3388,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025009</t>
+          <t>https://artportalen.se/Sighting/135025196</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135025010</v>
+        <v>119645924</v>
       </c>
       <c r="B26" t="n">
-        <v>99247</v>
+        <v>58085</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3416,46 +3405,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219798</v>
+        <v>205976</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bäl Gute 1:46 A 27759-2026., Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>719345</v>
+        <v>719342</v>
       </c>
       <c r="R26" t="n">
-        <v>6395079</v>
+        <v>6395013</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3479,12 +3459,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3495,36 +3475,31 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Ängsbarrskog, träd på socklar.</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025010</t>
+          <t>https://artportalen.se/Sighting/119645924</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135025011</v>
+        <v>135025043</v>
       </c>
       <c r="B27" t="n">
-        <v>99247</v>
+        <v>111342</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3532,43 +3507,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219798</v>
+        <v>219677</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bäl Gute 1:46 A 27759-2026., Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>719364</v>
+        <v>719351</v>
       </c>
       <c r="R27" t="n">
-        <v>6395036</v>
+        <v>6394940</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3603,6 +3569,11 @@
           <t>2026-06-30</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Flera grova tallar mot NO.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3631,16 +3602,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025011</t>
+          <t>https://artportalen.se/Sighting/135025043</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135025026</v>
+        <v>135025047</v>
       </c>
       <c r="B28" t="n">
-        <v>99247</v>
+        <v>111342</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3648,43 +3619,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219798</v>
+        <v>219677</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bäl Gute 1:46 A 27759-2026., Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>719361</v>
+        <v>719372</v>
       </c>
       <c r="R28" t="n">
-        <v>6395021</v>
+        <v>6394909</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3719,6 +3681,11 @@
           <t>2026-06-30</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>I döende björk.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3730,7 +3697,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Ängsbarrskog, träd på socklar. Vid mindre dike med vatten.</t>
+          <t>Ängsbarrskog, träd på socklar.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3747,16 +3714,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025026</t>
+          <t>https://artportalen.se/Sighting/135025047</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135025029</v>
+        <v>135025061</v>
       </c>
       <c r="B29" t="n">
-        <v>99247</v>
+        <v>111342</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3764,26 +3731,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219798</v>
+        <v>219677</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3797,10 +3764,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>719363</v>
+        <v>719423</v>
       </c>
       <c r="R29" t="n">
-        <v>6395012</v>
+        <v>6394896</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3835,6 +3802,11 @@
           <t>2026-06-30</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>I träd med Snitsel hänsyn mot N.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3863,16 +3835,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025029</t>
+          <t>https://artportalen.se/Sighting/135025061</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135025045</v>
+        <v>135025070</v>
       </c>
       <c r="B30" t="n">
-        <v>99247</v>
+        <v>111342</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3880,43 +3852,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219798</v>
+        <v>219677</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Bäl Gute 1:46 A 27759-2026., Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>719363</v>
+        <v>719318</v>
       </c>
       <c r="R30" t="n">
-        <v>6394922</v>
+        <v>6394792</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3953,7 +3916,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Snitsel hänsyn mot N.</t>
+          <t>Dike SO. I träd.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3967,7 +3930,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Ängsbarrskog, träd på socklar.</t>
+          <t>Ängsbarrskog, träd på socklar. Närmast sumpskog.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3984,16 +3947,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025045</t>
+          <t>https://artportalen.se/Sighting/135025070</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135025055</v>
+        <v>135025079</v>
       </c>
       <c r="B31" t="n">
-        <v>99247</v>
+        <v>111342</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4001,43 +3964,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219798</v>
+        <v>219677</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Bäl Gute 1:46 A 27759-2026., Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>719404</v>
+        <v>719282</v>
       </c>
       <c r="R31" t="n">
-        <v>6394899</v>
+        <v>6394872</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4074,7 +4028,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Snitsel hänsyn mot N.</t>
+          <t>I träd.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4088,7 +4042,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Ängsbarrskog, träd på socklar.</t>
+          <t>Ängsbarrskog.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4105,48 +4059,48 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025055</t>
+          <t>https://artportalen.se/Sighting/135025079</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135025059</v>
+        <v>135025001</v>
       </c>
       <c r="B32" t="n">
-        <v>99247</v>
+        <v>111556</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219798</v>
+        <v>219711</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4155,10 +4109,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>719419</v>
+        <v>719343</v>
       </c>
       <c r="R32" t="n">
-        <v>6394897</v>
+        <v>6395110</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4193,11 +4147,6 @@
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Snitsel hänsyn mot N.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4226,13 +4175,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025059</t>
+          <t>https://artportalen.se/Sighting/135025001</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135025063</v>
+        <v>135025002</v>
       </c>
       <c r="B33" t="n">
         <v>99247</v>
@@ -4262,7 +4211,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4276,10 +4225,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>719423</v>
+        <v>719343</v>
       </c>
       <c r="R33" t="n">
-        <v>6394896</v>
+        <v>6395110</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4314,11 +4263,6 @@
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Snitsel hänsyn mot N.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4347,13 +4291,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025063</t>
+          <t>https://artportalen.se/Sighting/135025002</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135025066</v>
+        <v>135025009</v>
       </c>
       <c r="B34" t="n">
         <v>99247</v>
@@ -4383,7 +4327,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4397,10 +4341,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>719456</v>
+        <v>719338</v>
       </c>
       <c r="R34" t="n">
-        <v>6394904</v>
+        <v>6395097</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4435,11 +4379,6 @@
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Snitsel hänsyn mot N.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4468,16 +4407,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025066</t>
+          <t>https://artportalen.se/Sighting/135025009</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135025003</v>
+        <v>135025010</v>
       </c>
       <c r="B35" t="n">
-        <v>99293</v>
+        <v>99247</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4485,34 +4424,43 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219847</v>
+        <v>219798</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Bäl Gute 1:46 A 27759-2026., Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>719343</v>
+        <v>719345</v>
       </c>
       <c r="R35" t="n">
-        <v>6395110</v>
+        <v>6395079</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4575,16 +4523,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025003</t>
+          <t>https://artportalen.se/Sighting/135025010</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135025006</v>
+        <v>135025011</v>
       </c>
       <c r="B36" t="n">
-        <v>99293</v>
+        <v>99247</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4592,34 +4540,43 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219847</v>
+        <v>219798</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Bäl Gute 1:46 A 27759-2026., Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>719338</v>
+        <v>719364</v>
       </c>
       <c r="R36" t="n">
-        <v>6395097</v>
+        <v>6395036</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4682,16 +4639,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025006</t>
+          <t>https://artportalen.se/Sighting/135025011</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135025013</v>
+        <v>135025026</v>
       </c>
       <c r="B37" t="n">
-        <v>99293</v>
+        <v>99247</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4699,34 +4656,43 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219847</v>
+        <v>219798</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bäl Gute 1:46 A 27759-2026., Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>719364</v>
+        <v>719361</v>
       </c>
       <c r="R37" t="n">
-        <v>6395036</v>
+        <v>6395021</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4772,7 +4738,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Ängsbarrskog, träd på socklar.</t>
+          <t>Ängsbarrskog, träd på socklar. Vid mindre dike med vatten.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4789,16 +4755,16 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025013</t>
+          <t>https://artportalen.se/Sighting/135025026</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135025016</v>
+        <v>135025029</v>
       </c>
       <c r="B38" t="n">
-        <v>99293</v>
+        <v>99247</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4806,34 +4772,43 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219847</v>
+        <v>219798</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Bäl Gute 1:46 A 27759-2026., Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>719373</v>
+        <v>719363</v>
       </c>
       <c r="R38" t="n">
-        <v>6395035</v>
+        <v>6395012</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4896,16 +4871,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025016</t>
+          <t>https://artportalen.se/Sighting/135025029</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135025033</v>
+        <v>135025045</v>
       </c>
       <c r="B39" t="n">
-        <v>99293</v>
+        <v>99247</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4913,34 +4888,43 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219847</v>
+        <v>219798</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Bäl Gute 1:46 A 27759-2026., Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>719352</v>
+        <v>719363</v>
       </c>
       <c r="R39" t="n">
-        <v>6394967</v>
+        <v>6394922</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4975,6 +4959,11 @@
           <t>2026-06-30</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Snitsel hänsyn mot N.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5003,16 +4992,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025033</t>
+          <t>https://artportalen.se/Sighting/135025045</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135025050</v>
+        <v>135025055</v>
       </c>
       <c r="B40" t="n">
-        <v>99293</v>
+        <v>99247</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5020,34 +5009,43 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219847</v>
+        <v>219798</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Bäl Gute 1:46 A 27759-2026., Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>719372</v>
+        <v>719404</v>
       </c>
       <c r="R40" t="n">
-        <v>6394909</v>
+        <v>6394899</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5082,6 +5080,11 @@
           <t>2026-06-30</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Snitsel hänsyn mot N.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5110,16 +5113,16 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025050</t>
+          <t>https://artportalen.se/Sighting/135025055</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135025076</v>
+        <v>135025059</v>
       </c>
       <c r="B41" t="n">
-        <v>99293</v>
+        <v>99247</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5127,31 +5130,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219847</v>
+        <v>219798</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5160,10 +5163,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>719291</v>
+        <v>719419</v>
       </c>
       <c r="R41" t="n">
-        <v>6394840</v>
+        <v>6394897</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5198,6 +5201,11 @@
           <t>2026-06-30</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Snitsel hänsyn mot N.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5209,7 +5217,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Ängsbarrskog, träd på socklar..</t>
+          <t>Ängsbarrskog, träd på socklar.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5226,16 +5234,16 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025076</t>
+          <t>https://artportalen.se/Sighting/135025059</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135025077</v>
+        <v>135025063</v>
       </c>
       <c r="B42" t="n">
-        <v>99293</v>
+        <v>99247</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5243,31 +5251,31 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219847</v>
+        <v>219798</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5276,10 +5284,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>719281</v>
+        <v>719423</v>
       </c>
       <c r="R42" t="n">
-        <v>6394853</v>
+        <v>6394896</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5314,6 +5322,11 @@
           <t>2026-06-30</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Snitsel hänsyn mot N.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5325,7 +5338,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Ängsbarrskog.</t>
+          <t>Ängsbarrskog, träd på socklar.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5342,16 +5355,16 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025077</t>
+          <t>https://artportalen.se/Sighting/135025063</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135025080</v>
+        <v>135025066</v>
       </c>
       <c r="B43" t="n">
-        <v>99293</v>
+        <v>99247</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5359,31 +5372,31 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219847</v>
+        <v>219798</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5392,10 +5405,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>719282</v>
+        <v>719456</v>
       </c>
       <c r="R43" t="n">
-        <v>6394872</v>
+        <v>6394904</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5430,6 +5443,11 @@
           <t>2026-06-30</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Snitsel hänsyn mot N.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5441,7 +5459,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Ängsbarrskog.</t>
+          <t>Ängsbarrskog, träd på socklar.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5458,16 +5476,16 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025080</t>
+          <t>https://artportalen.se/Sighting/135025066</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135025021</v>
+        <v>135025003</v>
       </c>
       <c r="B44" t="n">
-        <v>99307</v>
+        <v>99293</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5475,43 +5493,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219875</v>
+        <v>219847</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Bäl Gute 1:46 A 27759-2026., Gtl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>719364</v>
+        <v>719343</v>
       </c>
       <c r="R44" t="n">
-        <v>6395036</v>
+        <v>6395110</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5574,16 +5583,16 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025021</t>
+          <t>https://artportalen.se/Sighting/135025003</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135025025</v>
+        <v>135025006</v>
       </c>
       <c r="B45" t="n">
-        <v>99307</v>
+        <v>99293</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5591,43 +5600,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219875</v>
+        <v>219847</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Bäl Gute 1:46 A 27759-2026., Gtl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>719361</v>
+        <v>719338</v>
       </c>
       <c r="R45" t="n">
-        <v>6395021</v>
+        <v>6395097</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5673,7 +5673,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Ängsbarrskog, träd på socklar. Vid mindre dike med vatten.</t>
+          <t>Ängsbarrskog, träd på socklar.</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5690,38 +5690,38 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025025</t>
+          <t>https://artportalen.se/Sighting/135025006</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135025015</v>
+        <v>135025013</v>
       </c>
       <c r="B46" t="n">
-        <v>110242</v>
+        <v>99293</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5731,10 +5731,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>719373</v>
+        <v>719364</v>
       </c>
       <c r="R46" t="n">
-        <v>6395035</v>
+        <v>6395036</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5797,38 +5797,38 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025015</t>
+          <t>https://artportalen.se/Sighting/135025013</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135025024</v>
+        <v>135025016</v>
       </c>
       <c r="B47" t="n">
-        <v>110242</v>
+        <v>99293</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5838,10 +5838,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>719361</v>
+        <v>719373</v>
       </c>
       <c r="R47" t="n">
-        <v>6395021</v>
+        <v>6395035</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5887,7 +5887,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Ängsbarrskog, träd på socklar. Vid mindre dike med vatten.</t>
+          <t>Ängsbarrskog, träd på socklar.</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5904,38 +5904,38 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025024</t>
+          <t>https://artportalen.se/Sighting/135025016</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135025048</v>
+        <v>135025033</v>
       </c>
       <c r="B48" t="n">
-        <v>110242</v>
+        <v>99293</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5945,10 +5945,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>719372</v>
+        <v>719352</v>
       </c>
       <c r="R48" t="n">
-        <v>6394909</v>
+        <v>6394967</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6011,38 +6011,38 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025048</t>
+          <t>https://artportalen.se/Sighting/135025033</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135025058</v>
+        <v>135025050</v>
       </c>
       <c r="B49" t="n">
-        <v>110242</v>
+        <v>99293</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6052,10 +6052,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>719419</v>
+        <v>719372</v>
       </c>
       <c r="R49" t="n">
-        <v>6394897</v>
+        <v>6394909</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6090,11 +6090,6 @@
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Spridd i hela skogen.</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6106,7 +6101,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Ängsbarrskog, träd på socklar. Närmast sumpskog.</t>
+          <t>Ängsbarrskog, träd på socklar.</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6123,51 +6118,60 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025058</t>
+          <t>https://artportalen.se/Sighting/135025050</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135025069</v>
+        <v>135025076</v>
       </c>
       <c r="B50" t="n">
-        <v>110242</v>
+        <v>99293</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Bäl Gute 1:46 A 27759-2026., Gtl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>719440</v>
+        <v>719291</v>
       </c>
       <c r="R50" t="n">
-        <v>6394836</v>
+        <v>6394840</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6202,11 +6206,6 @@
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Spridd i hela skogen.</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6218,7 +6217,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Ängsbarrskog, träd på socklar. Närmast sumpskog.</t>
+          <t>Ängsbarrskog, träd på socklar..</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6235,51 +6234,60 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025069</t>
+          <t>https://artportalen.se/Sighting/135025076</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135025073</v>
+        <v>135025077</v>
       </c>
       <c r="B51" t="n">
-        <v>110242</v>
+        <v>99293</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Bäl Gute 1:46 A 27759-2026., Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>719313</v>
+        <v>719281</v>
       </c>
       <c r="R51" t="n">
-        <v>6394797</v>
+        <v>6394853</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6314,11 +6322,6 @@
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6330,7 +6333,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Ängsbarrskog, träd på socklar. Närmast sumpskog.</t>
+          <t>Ängsbarrskog.</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6347,51 +6350,60 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025073</t>
+          <t>https://artportalen.se/Sighting/135025077</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135025074</v>
+        <v>135025080</v>
       </c>
       <c r="B52" t="n">
-        <v>110242</v>
+        <v>99293</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bäl Gute 1:46 A 27759-2026., Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>719301</v>
+        <v>719282</v>
       </c>
       <c r="R52" t="n">
-        <v>6394804</v>
+        <v>6394872</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6437,7 +6449,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Ängsbarrskog, träd på socklar..</t>
+          <t>Ängsbarrskog.</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6454,54 +6466,63 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025074</t>
+          <t>https://artportalen.se/Sighting/135025080</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135025083</v>
+        <v>135025021</v>
       </c>
       <c r="B53" t="n">
-        <v>110242</v>
+        <v>99307</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220299</v>
+        <v>219875</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Bäl Gute 1:46 A 27759-2026., Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>719274</v>
+        <v>719364</v>
       </c>
       <c r="R53" t="n">
-        <v>6394901</v>
+        <v>6395036</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6533,11 +6554,6 @@
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6549,7 +6565,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>Ängsbarrskog.</t>
+          <t>Ängsbarrskog, träd på socklar.</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6566,54 +6582,63 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025083</t>
+          <t>https://artportalen.se/Sighting/135025021</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135025082</v>
+        <v>135025025</v>
       </c>
       <c r="B54" t="n">
-        <v>106976</v>
+        <v>99307</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220785</v>
+        <v>219875</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Bäl Gute 1:46 A 27759-2026., Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>719274</v>
+        <v>719361</v>
       </c>
       <c r="R54" t="n">
-        <v>6394901</v>
+        <v>6395021</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6656,7 +6681,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Ängsbarrskog.</t>
+          <t>Ängsbarrskog, träd på socklar. Vid mindre dike med vatten.</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6673,16 +6698,16 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025082</t>
+          <t>https://artportalen.se/Sighting/135025025</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135025004</v>
+        <v>135025015</v>
       </c>
       <c r="B55" t="n">
-        <v>102394</v>
+        <v>110242</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6690,43 +6715,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221235</v>
+        <v>220299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Bäl Gute 1:46 A 27759-2026., Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>719343</v>
+        <v>719373</v>
       </c>
       <c r="R55" t="n">
-        <v>6395110</v>
+        <v>6395035</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6789,16 +6805,16 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025004</t>
+          <t>https://artportalen.se/Sighting/135025015</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135025008</v>
+        <v>135025024</v>
       </c>
       <c r="B56" t="n">
-        <v>102394</v>
+        <v>110242</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6806,43 +6822,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221235</v>
+        <v>220299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Bäl Gute 1:46 A 27759-2026., Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>719338</v>
+        <v>719361</v>
       </c>
       <c r="R56" t="n">
-        <v>6395097</v>
+        <v>6395021</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6888,7 +6895,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Ängsbarrskog, träd på socklar.</t>
+          <t>Ängsbarrskog, träd på socklar. Vid mindre dike med vatten.</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -6905,16 +6912,16 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025008</t>
+          <t>https://artportalen.se/Sighting/135025024</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135025012</v>
+        <v>135025048</v>
       </c>
       <c r="B57" t="n">
-        <v>102394</v>
+        <v>110242</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6922,43 +6929,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221235</v>
+        <v>220299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Bäl Gute 1:46 A 27759-2026., Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>719364</v>
+        <v>719372</v>
       </c>
       <c r="R57" t="n">
-        <v>6395036</v>
+        <v>6394909</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7021,16 +7019,16 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025012</t>
+          <t>https://artportalen.se/Sighting/135025048</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135025028</v>
+        <v>135025058</v>
       </c>
       <c r="B58" t="n">
-        <v>102394</v>
+        <v>110242</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7038,43 +7036,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221235</v>
+        <v>220299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Bäl Gute 1:46 A 27759-2026., Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>719363</v>
+        <v>719419</v>
       </c>
       <c r="R58" t="n">
-        <v>6395012</v>
+        <v>6394897</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7109,6 +7098,11 @@
           <t>2026-06-30</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Spridd i hela skogen.</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7120,7 +7114,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>Ängsbarrskog, träd på socklar.</t>
+          <t>Ängsbarrskog, träd på socklar. Närmast sumpskog.</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7137,16 +7131,16 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025028</t>
+          <t>https://artportalen.se/Sighting/135025058</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135025035</v>
+        <v>135025069</v>
       </c>
       <c r="B59" t="n">
-        <v>102394</v>
+        <v>110242</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7154,43 +7148,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221235</v>
+        <v>220299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Bäl Gute 1:46 A 27759-2026., Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>719352</v>
+        <v>719440</v>
       </c>
       <c r="R59" t="n">
-        <v>6394967</v>
+        <v>6394836</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7225,6 +7210,11 @@
           <t>2026-06-30</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Spridd i hela skogen.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -7236,7 +7226,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>Ängsbarrskog, träd på socklar.</t>
+          <t>Ängsbarrskog, träd på socklar. Närmast sumpskog.</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7253,16 +7243,16 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025035</t>
+          <t>https://artportalen.se/Sighting/135025069</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135025038</v>
+        <v>135025073</v>
       </c>
       <c r="B60" t="n">
-        <v>102394</v>
+        <v>110242</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7270,21 +7260,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221235</v>
+        <v>220299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7294,10 +7284,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>719331</v>
+        <v>719313</v>
       </c>
       <c r="R60" t="n">
-        <v>6394934</v>
+        <v>6394797</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7332,6 +7322,11 @@
           <t>2026-06-30</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -7343,7 +7338,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>Ängsbarrskog, träd på socklar.</t>
+          <t>Ängsbarrskog, träd på socklar. Närmast sumpskog.</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7360,16 +7355,16 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025038</t>
+          <t>https://artportalen.se/Sighting/135025073</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135025062</v>
+        <v>135025074</v>
       </c>
       <c r="B61" t="n">
-        <v>102394</v>
+        <v>110242</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7377,43 +7372,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221235</v>
+        <v>220299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Bäl Gute 1:46 A 27759-2026., Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>719423</v>
+        <v>719301</v>
       </c>
       <c r="R61" t="n">
-        <v>6394896</v>
+        <v>6394804</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7448,11 +7434,6 @@
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Snitsel hänsyn mot N.</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -7464,7 +7445,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Ängsbarrskog, träd på socklar.</t>
+          <t>Ängsbarrskog, träd på socklar..</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7481,33 +7462,33 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025062</t>
+          <t>https://artportalen.se/Sighting/135025074</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>112363301</v>
+        <v>135025083</v>
       </c>
       <c r="B62" t="n">
-        <v>97983</v>
+        <v>110242</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221945</v>
+        <v>220299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -7518,14 +7499,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Säggeby Tjaut, Gtl</t>
+          <t>Bäl Gute 1:46 A 27759-2026., Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>719397</v>
+        <v>719274</v>
       </c>
       <c r="R62" t="n">
-        <v>6395045</v>
+        <v>6394901</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7552,12 +7533,17 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7568,48 +7554,53 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>Ängsbarrskog.</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112363301</t>
+          <t>https://artportalen.se/Sighting/135025083</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135025000</v>
+        <v>135025082</v>
       </c>
       <c r="B63" t="n">
-        <v>103840</v>
+        <v>106976</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>222002</v>
+        <v>220785</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -7617,29 +7608,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Bäl Gute 1:46 A 27759-2026., Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>719343</v>
+        <v>719274</v>
       </c>
       <c r="R63" t="n">
-        <v>6395110</v>
+        <v>6394901</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7682,7 +7664,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>Ängsbarrskog, träd på socklar.</t>
+          <t>Ängsbarrskog.</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7699,43 +7681,43 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025000</t>
+          <t>https://artportalen.se/Sighting/135025082</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135025037</v>
+        <v>135025004</v>
       </c>
       <c r="B64" t="n">
-        <v>99075</v>
+        <v>102394</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>223049</v>
+        <v>221235</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7749,10 +7731,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>719331</v>
+        <v>719343</v>
       </c>
       <c r="R64" t="n">
-        <v>6394934</v>
+        <v>6395110</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7787,11 +7769,6 @@
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>6-bladig.</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -7820,54 +7797,63 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025037</t>
+          <t>https://artportalen.se/Sighting/135025004</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135025085</v>
+        <v>135025008</v>
       </c>
       <c r="B65" t="n">
-        <v>99075</v>
+        <v>102394</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>223049</v>
+        <v>221235</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Bäl Gute 1:46., Gtl</t>
+          <t>Bäl Gute 1:46 A 27759-2026., Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>719259</v>
+        <v>719338</v>
       </c>
       <c r="R65" t="n">
-        <v>6394903</v>
+        <v>6395097</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7899,11 +7885,6 @@
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Även 5-bladig.</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7915,7 +7896,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>Tallplantage.</t>
+          <t>Ängsbarrskog, träd på socklar.</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -7932,43 +7913,43 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025085</t>
+          <t>https://artportalen.se/Sighting/135025008</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135025071</v>
+        <v>135025012</v>
       </c>
       <c r="B66" t="n">
-        <v>103565</v>
+        <v>102394</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>223248</v>
+        <v>221235</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lundalm</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ulmus minor</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Mill.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -7982,10 +7963,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>719318</v>
+        <v>719364</v>
       </c>
       <c r="R66" t="n">
-        <v>6394792</v>
+        <v>6395036</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -8020,11 +8001,6 @@
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Dike SO.</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -8036,7 +8012,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>Ängsbarrskog, träd på socklar. Närmast sumpskog.</t>
+          <t>Ängsbarrskog, träd på socklar.</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8053,43 +8029,43 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025071</t>
+          <t>https://artportalen.se/Sighting/135025012</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135024998</v>
+        <v>135025028</v>
       </c>
       <c r="B67" t="n">
-        <v>99187</v>
+        <v>102394</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>223591</v>
+        <v>221235</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8103,10 +8079,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>719284</v>
+        <v>719363</v>
       </c>
       <c r="R67" t="n">
-        <v>6395138</v>
+        <v>6395012</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -8141,18 +8117,12 @@
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Vid gräns mot Gute 6:1.</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -8175,43 +8145,43 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135024998</t>
+          <t>https://artportalen.se/Sighting/135025028</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135025005</v>
+        <v>135025035</v>
       </c>
       <c r="B68" t="n">
-        <v>99187</v>
+        <v>102394</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>223591</v>
+        <v>221235</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -8225,10 +8195,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>719343</v>
+        <v>719352</v>
       </c>
       <c r="R68" t="n">
-        <v>6395110</v>
+        <v>6394967</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8269,7 +8239,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8292,60 +8261,51 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025005</t>
+          <t>https://artportalen.se/Sighting/135025035</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135025022</v>
+        <v>135025038</v>
       </c>
       <c r="B69" t="n">
-        <v>99187</v>
+        <v>102394</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>223591</v>
+        <v>221235</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Bäl Gute 1:46 A 27759-2026., Gtl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>719364</v>
+        <v>719331</v>
       </c>
       <c r="R69" t="n">
-        <v>6395036</v>
+        <v>6394934</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8386,7 +8346,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8409,43 +8368,43 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025022</t>
+          <t>https://artportalen.se/Sighting/135025038</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135025027</v>
+        <v>135025062</v>
       </c>
       <c r="B70" t="n">
-        <v>99187</v>
+        <v>102394</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>223591</v>
+        <v>221235</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8459,10 +8418,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>719361</v>
+        <v>719423</v>
       </c>
       <c r="R70" t="n">
-        <v>6395021</v>
+        <v>6394896</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8497,19 +8456,23 @@
           <t>2026-06-30</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Snitsel hänsyn mot N.</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>Ängsbarrskog, träd på socklar. Vid mindre dike med vatten.</t>
+          <t>Ängsbarrskog, träd på socklar.</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8526,63 +8489,54 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025027</t>
+          <t>https://artportalen.se/Sighting/135025062</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135025034</v>
+        <v>137124398</v>
       </c>
       <c r="B71" t="n">
-        <v>99187</v>
+        <v>102488</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>223591</v>
+        <v>221235</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Bäl Gute 1:46 A 27759-2026., Gtl</t>
+          <t>Bål Gute, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>719352</v>
+        <v>719356</v>
       </c>
       <c r="R71" t="n">
-        <v>6394967</v>
+        <v>6395104</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8606,12 +8560,22 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8620,39 +8584,33 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AI71" t="inlineStr">
-        <is>
-          <t>Ängsbarrskog, träd på socklar.</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025034</t>
+          <t>https://artportalen.se/Sighting/137124398</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135025046</v>
+        <v>112363301</v>
       </c>
       <c r="B72" t="n">
-        <v>99187</v>
+        <v>97983</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8660,46 +8618,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>223591</v>
+        <v>221945</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Bäl Gute 1:46 A 27759-2026., Gtl</t>
+          <t>Säggeby Tjaut, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>719363</v>
+        <v>719397</v>
       </c>
       <c r="R72" t="n">
-        <v>6394922</v>
+        <v>6395045</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8723,12 +8672,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8737,39 +8686,33 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>Ängsbarrskog, träd på socklar.</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025046</t>
+          <t>https://artportalen.se/Sighting/112363301</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135025049</v>
+        <v>135025000</v>
       </c>
       <c r="B73" t="n">
-        <v>99187</v>
+        <v>103840</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8777,26 +8720,26 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>223591</v>
+        <v>222002</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -8810,10 +8753,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>719372</v>
+        <v>719343</v>
       </c>
       <c r="R73" t="n">
-        <v>6394909</v>
+        <v>6395110</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8854,7 +8797,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8877,16 +8819,16 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025049</t>
+          <t>https://artportalen.se/Sighting/135025000</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135025053</v>
+        <v>135025037</v>
       </c>
       <c r="B74" t="n">
-        <v>99187</v>
+        <v>99075</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8894,26 +8836,26 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>223591</v>
+        <v>223049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -8927,10 +8869,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>719389</v>
+        <v>719331</v>
       </c>
       <c r="R74" t="n">
-        <v>6394903</v>
+        <v>6394934</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8967,7 +8909,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Snitsel hänsyn mot N.</t>
+          <t>6-bladig.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8976,7 +8918,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8999,16 +8940,16 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025053</t>
+          <t>https://artportalen.se/Sighting/135025037</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135025075</v>
+        <v>135025085</v>
       </c>
       <c r="B75" t="n">
-        <v>99187</v>
+        <v>99075</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9016,46 +8957,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>223591</v>
+        <v>223049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Bäl Gute 1:46 A 27759-2026., Gtl</t>
+          <t>Bäl Gute 1:46., Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>719301</v>
+        <v>719259</v>
       </c>
       <c r="R75" t="n">
-        <v>6394804</v>
+        <v>6394903</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9087,6 +9019,11 @@
           <t>2026-06-30</t>
         </is>
       </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Även 5-bladig.</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -9098,7 +9035,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>Ängsbarrskog, träd på socklar..</t>
+          <t>Tallplantage.</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9115,43 +9052,43 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025075</t>
+          <t>https://artportalen.se/Sighting/135025085</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>135025084</v>
+        <v>135025071</v>
       </c>
       <c r="B76" t="n">
-        <v>99187</v>
+        <v>103565</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>223591</v>
+        <v>223248</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Lundalm</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Ulmus minor</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>Mill.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -9165,13 +9102,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>719274</v>
+        <v>719318</v>
       </c>
       <c r="R76" t="n">
-        <v>6394901</v>
+        <v>6394792</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9203,6 +9140,11 @@
           <t>2026-06-30</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Dike SO.</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -9214,7 +9156,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>Ängsbarrskog.</t>
+          <t>Ängsbarrskog, träd på socklar. Närmast sumpskog.</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9231,13 +9173,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025084</t>
+          <t>https://artportalen.se/Sighting/135025071</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135025087</v>
+        <v>135024998</v>
       </c>
       <c r="B77" t="n">
         <v>99187</v>
@@ -9267,7 +9209,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -9277,17 +9219,17 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Bäl Gute 1:46., Gtl</t>
+          <t>Bäl Gute 1:46 A 27759-2026., Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>719259</v>
+        <v>719284</v>
       </c>
       <c r="R77" t="n">
-        <v>6394903</v>
+        <v>6395138</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9319,18 +9261,24 @@
           <t>2026-06-30</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Vid gräns mot Gute 6:1.</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>Tallplantage.</t>
+          <t>Ängsbarrskog, träd på socklar.</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9347,16 +9295,16 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135025087</t>
+          <t>https://artportalen.se/Sighting/135024998</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>74112555</v>
+        <v>135025005</v>
       </c>
       <c r="B78" t="n">
-        <v>80392</v>
+        <v>99187</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9364,37 +9312,46 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>229497</v>
+        <v>223591</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Bäl-Gane, Gtl</t>
+          <t>Bäl Gute 1:46 A 27759-2026., Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>719321</v>
+        <v>719343</v>
       </c>
       <c r="R78" t="n">
-        <v>6395125</v>
+        <v>6395110</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9418,12 +9375,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2018-09-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2018-10-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9432,33 +9389,39 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>Ängsbarrskog, träd på socklar.</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/74112555</t>
+          <t>https://artportalen.se/Sighting/135025005</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>74112596</v>
+        <v>135025022</v>
       </c>
       <c r="B79" t="n">
-        <v>80992</v>
+        <v>99187</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9466,37 +9429,46 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>230185</v>
+        <v>223591</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Bäl-Gane, Gtl</t>
+          <t>Bäl Gute 1:46 A 27759-2026., Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>719695</v>
+        <v>719364</v>
       </c>
       <c r="R79" t="n">
-        <v>6395029</v>
+        <v>6395036</v>
       </c>
       <c r="S79" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9515,17 +9487,17 @@
       </c>
       <c r="W79" t="inlineStr">
         <is>
-          <t>Källunge</t>
+          <t>Bäl</t>
         </is>
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2018-09-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2018-10-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9534,67 +9506,86 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>Ängsbarrskog, träd på socklar.</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/74112596</t>
+          <t>https://artportalen.se/Sighting/135025022</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>74112674</v>
+        <v>135025027</v>
       </c>
       <c r="B80" t="n">
-        <v>75312</v>
+        <v>99187</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6000146</v>
+        <v>223591</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Coniocarpon fallax</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Grube</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Bäl-Gane, Gtl</t>
+          <t>Bäl Gute 1:46 A 27759-2026., Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>719426</v>
+        <v>719361</v>
       </c>
       <c r="R80" t="n">
-        <v>6394937</v>
+        <v>6395021</v>
       </c>
       <c r="S80" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9618,12 +9609,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2018-09-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2018-10-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9632,82 +9623,86 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>blandsumpskog</t>
-        </is>
-      </c>
-      <c r="AL80" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>ask</t>
+          <t>Ängsbarrskog, träd på socklar. Vid mindre dike med vatten.</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/74112674</t>
+          <t>https://artportalen.se/Sighting/135025027</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>74112675</v>
+        <v>135025034</v>
       </c>
       <c r="B81" t="n">
-        <v>75312</v>
+        <v>99187</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6000146</v>
+        <v>223591</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Coniocarpon fallax</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Grube</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Bäl-Gane, Gtl</t>
+          <t>Bäl Gute 1:46 A 27759-2026., Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>719379</v>
+        <v>719352</v>
       </c>
       <c r="R81" t="n">
-        <v>6394918</v>
+        <v>6394967</v>
       </c>
       <c r="S81" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9731,12 +9726,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2018-09-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2018-10-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9745,82 +9740,86 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>blandsumpskog</t>
-        </is>
-      </c>
-      <c r="AL81" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>ask</t>
+          <t>Ängsbarrskog, träd på socklar.</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/74112675</t>
+          <t>https://artportalen.se/Sighting/135025034</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>74112676</v>
+        <v>135025046</v>
       </c>
       <c r="B82" t="n">
-        <v>75312</v>
+        <v>99187</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6000146</v>
+        <v>223591</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Coniocarpon fallax</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Grube</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Bäl-Gane, Gtl</t>
+          <t>Bäl Gute 1:46 A 27759-2026., Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>719376</v>
+        <v>719363</v>
       </c>
       <c r="R82" t="n">
-        <v>6394943</v>
+        <v>6394922</v>
       </c>
       <c r="S82" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9844,12 +9843,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2018-09-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2018-10-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9858,82 +9857,86 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>blandsumpskog</t>
-        </is>
-      </c>
-      <c r="AL82" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>ask</t>
+          <t>Ängsbarrskog, träd på socklar.</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/74112676</t>
+          <t>https://artportalen.se/Sighting/135025046</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>74112677</v>
+        <v>135025049</v>
       </c>
       <c r="B83" t="n">
-        <v>75312</v>
+        <v>99187</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6000146</v>
+        <v>223591</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Coniocarpon fallax</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Grube</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Bäl-Gane, Gtl</t>
+          <t>Bäl Gute 1:46 A 27759-2026., Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>719367</v>
+        <v>719372</v>
       </c>
       <c r="R83" t="n">
-        <v>6394945</v>
+        <v>6394909</v>
       </c>
       <c r="S83" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9957,12 +9960,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2018-09-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2018-10-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9971,82 +9974,86 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>blandsumpskog</t>
-        </is>
-      </c>
-      <c r="AL83" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>ask</t>
+          <t>Ängsbarrskog, träd på socklar.</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/74112677</t>
+          <t>https://artportalen.se/Sighting/135025049</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>74112678</v>
+        <v>135025053</v>
       </c>
       <c r="B84" t="n">
-        <v>75312</v>
+        <v>99187</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6000146</v>
+        <v>223591</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Coniocarpon fallax</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Grube</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Bäl-Gane, Gtl</t>
+          <t>Bäl Gute 1:46 A 27759-2026., Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>719367</v>
+        <v>719389</v>
       </c>
       <c r="R84" t="n">
-        <v>6394954</v>
+        <v>6394903</v>
       </c>
       <c r="S84" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10070,12 +10077,17 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2018-09-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2018-10-27</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Snitsel hänsyn mot N.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10084,82 +10096,86 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>blandsumpskog</t>
-        </is>
-      </c>
-      <c r="AL84" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>ask</t>
+          <t>Ängsbarrskog, träd på socklar.</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/74112678</t>
+          <t>https://artportalen.se/Sighting/135025053</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>74112679</v>
+        <v>135025075</v>
       </c>
       <c r="B85" t="n">
-        <v>75312</v>
+        <v>99187</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6000146</v>
+        <v>223591</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Coniocarpon fallax</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Grube</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Bäl-Gane, Gtl</t>
+          <t>Bäl Gute 1:46 A 27759-2026., Gtl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>719405</v>
+        <v>719301</v>
       </c>
       <c r="R85" t="n">
-        <v>6394999</v>
+        <v>6394804</v>
       </c>
       <c r="S85" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10183,12 +10199,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2018-09-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2018-10-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10202,77 +10218,80 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>blandsumpskog</t>
-        </is>
-      </c>
-      <c r="AL85" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>ask</t>
+          <t>Ängsbarrskog, träd på socklar..</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/74112679</t>
+          <t>https://artportalen.se/Sighting/135025075</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>74112680</v>
+        <v>135025084</v>
       </c>
       <c r="B86" t="n">
-        <v>75312</v>
+        <v>99187</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6000146</v>
+        <v>223591</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Coniocarpon fallax</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Grube</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Bäl-Gane, Gtl</t>
+          <t>Bäl Gute 1:46 A 27759-2026., Gtl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>719361</v>
+        <v>719274</v>
       </c>
       <c r="R86" t="n">
-        <v>6395041</v>
+        <v>6394901</v>
       </c>
       <c r="S86" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10296,12 +10315,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2018-09-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2018-10-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10315,77 +10334,80 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>blandsumpskog</t>
-        </is>
-      </c>
-      <c r="AL86" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>ask</t>
+          <t>Ängsbarrskog.</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/74112680</t>
+          <t>https://artportalen.se/Sighting/135025084</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>74112681</v>
+        <v>135025087</v>
       </c>
       <c r="B87" t="n">
-        <v>75312</v>
+        <v>99187</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6000146</v>
+        <v>223591</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Coniocarpon fallax</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Grube</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Bäl-Gane, Gtl</t>
+          <t>Bäl Gute 1:46., Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>719350</v>
+        <v>719259</v>
       </c>
       <c r="R87" t="n">
-        <v>6395059</v>
+        <v>6394903</v>
       </c>
       <c r="S87" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10409,12 +10431,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2018-09-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2018-10-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10428,74 +10450,68 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>blandsumpskog</t>
-        </is>
-      </c>
-      <c r="AL87" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>ask</t>
+          <t>Tallplantage.</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/74112681</t>
+          <t>https://artportalen.se/Sighting/135025087</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>74112682</v>
+        <v>74112555</v>
       </c>
       <c r="B88" t="n">
-        <v>75312</v>
+        <v>80392</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6000146</v>
+        <v>229497</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Coniocarpon fallax</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Grube</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Bäl-Gane, Gtl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>719356</v>
+        <v>719321</v>
       </c>
       <c r="R88" t="n">
-        <v>6395063</v>
+        <v>6395125</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -10539,21 +10555,6 @@
       <c r="AG88" t="b">
         <v>0</v>
       </c>
-      <c r="AI88" t="inlineStr">
-        <is>
-          <t>blandsumpskog</t>
-        </is>
-      </c>
-      <c r="AL88" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
@@ -10568,47 +10569,51 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/74112682</t>
+          <t>https://artportalen.se/Sighting/74112555</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>74112683</v>
+        <v>74112596</v>
       </c>
       <c r="B89" t="n">
-        <v>75312</v>
+        <v>80992</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6000146</v>
+        <v>230185</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Coniocarpon fallax</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Grube</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Bäl-Gane, Gtl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>719361</v>
+        <v>719695</v>
       </c>
       <c r="R89" t="n">
-        <v>6395058</v>
+        <v>6395029</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -10630,7 +10635,7 @@
       </c>
       <c r="W89" t="inlineStr">
         <is>
-          <t>Bäl</t>
+          <t>Källunge</t>
         </is>
       </c>
       <c r="Y89" t="inlineStr">
@@ -10651,21 +10656,6 @@
       </c>
       <c r="AG89" t="b">
         <v>0</v>
-      </c>
-      <c r="AI89" t="inlineStr">
-        <is>
-          <t>blandsumpskog</t>
-        </is>
-      </c>
-      <c r="AL89" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
@@ -10681,50 +10671,54 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/74112683</t>
+          <t>https://artportalen.se/Sighting/74112596</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>74112684</v>
+        <v>137124401</v>
       </c>
       <c r="B90" t="n">
-        <v>75312</v>
+        <v>87445</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6000146</v>
+        <v>248956</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Coniocarpon fallax</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Grube</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Bäl-Gane, Gtl</t>
+          <t>Bål Gute, Gtl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>719363</v>
+        <v>719450</v>
       </c>
       <c r="R90" t="n">
-        <v>6395058</v>
+        <v>6394995</v>
       </c>
       <c r="S90" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10748,12 +10742,22 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2018-09-26</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2018-10-27</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10764,80 +10768,69 @@
       </c>
       <c r="AG90" t="b">
         <v>0</v>
-      </c>
-      <c r="AI90" t="inlineStr">
-        <is>
-          <t>blandsumpskog</t>
-        </is>
-      </c>
-      <c r="AL90" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/74112684</t>
+          <t>https://artportalen.se/Sighting/137124401</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>74112686</v>
+        <v>137124404</v>
       </c>
       <c r="B91" t="n">
-        <v>75312</v>
+        <v>87445</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6000146</v>
+        <v>248956</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Coniocarpon fallax</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Grube</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Bäl-Gane, Gtl</t>
+          <t>Bål Gute, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>719362</v>
+        <v>719452</v>
       </c>
       <c r="R91" t="n">
-        <v>6395060</v>
+        <v>6394769</v>
       </c>
       <c r="S91" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10861,12 +10854,22 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2018-09-26</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2018-10-27</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10877,43 +10880,28 @@
       </c>
       <c r="AG91" t="b">
         <v>0</v>
-      </c>
-      <c r="AI91" t="inlineStr">
-        <is>
-          <t>blandsumpskog</t>
-        </is>
-      </c>
-      <c r="AL91" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/74112686</t>
+          <t>https://artportalen.se/Sighting/137124404</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>74112687</v>
+        <v>74112674</v>
       </c>
       <c r="B92" t="n">
         <v>75312</v>
@@ -10944,10 +10932,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>719362</v>
+        <v>719426</v>
       </c>
       <c r="R92" t="n">
-        <v>6395063</v>
+        <v>6394937</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -11020,13 +11008,13 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/74112687</t>
+          <t>https://artportalen.se/Sighting/74112674</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>74112688</v>
+        <v>74112675</v>
       </c>
       <c r="B93" t="n">
         <v>75312</v>
@@ -11057,10 +11045,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>719360</v>
+        <v>719379</v>
       </c>
       <c r="R93" t="n">
-        <v>6395065</v>
+        <v>6394918</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -11133,13 +11121,13 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/74112688</t>
+          <t>https://artportalen.se/Sighting/74112675</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>74112689</v>
+        <v>74112676</v>
       </c>
       <c r="B94" t="n">
         <v>75312</v>
@@ -11170,10 +11158,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>719357</v>
+        <v>719376</v>
       </c>
       <c r="R94" t="n">
-        <v>6395067</v>
+        <v>6394943</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -11246,13 +11234,13 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/74112689</t>
+          <t>https://artportalen.se/Sighting/74112676</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>74112691</v>
+        <v>74112677</v>
       </c>
       <c r="B95" t="n">
         <v>75312</v>
@@ -11283,10 +11271,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>719357</v>
+        <v>719367</v>
       </c>
       <c r="R95" t="n">
-        <v>6395061</v>
+        <v>6394945</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -11359,51 +11347,47 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/74112691</t>
+          <t>https://artportalen.se/Sighting/74112677</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>74112639</v>
+        <v>74112678</v>
       </c>
       <c r="B96" t="n">
-        <v>87346</v>
+        <v>75312</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6003295</v>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Odörspindling</t>
-        </is>
+        <v>6000146</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Coniocarpon fallax</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Ach.) Grube</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Bäl-Gane, Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>719439</v>
+        <v>719367</v>
       </c>
       <c r="R96" t="n">
-        <v>6395001</v>
+        <v>6394954</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -11447,6 +11431,21 @@
       <c r="AG96" t="b">
         <v>0</v>
       </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AL96" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
@@ -11461,59 +11460,50 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/74112639</t>
+          <t>https://artportalen.se/Sighting/74112678</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>112363481</v>
+        <v>74112679</v>
       </c>
       <c r="B97" t="n">
-        <v>87346</v>
+        <v>75312</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6003295</v>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Odörspindling</t>
-        </is>
+        <v>6000146</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Coniocarpon fallax</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Ach.) Grube</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Säggeby Tjaut, Gtl</t>
+          <t>Bäl-Gane, Gtl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>719399</v>
+        <v>719405</v>
       </c>
       <c r="R97" t="n">
-        <v>6395044</v>
+        <v>6394999</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11537,12 +11527,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2018-09-26</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2018-10-27</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11553,22 +11543,1936 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AL97" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/74112679</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>74112680</v>
+      </c>
+      <c r="B98" t="n">
+        <v>75312</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>6000146</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Coniocarpon fallax</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Ach.) Grube</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Bäl-Gane, Gtl</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>719361</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6395041</v>
+      </c>
+      <c r="S98" t="n">
+        <v>25</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Bäl</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2018-09-26</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AL98" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74112680</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>74112681</v>
+      </c>
+      <c r="B99" t="n">
+        <v>75312</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>6000146</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Coniocarpon fallax</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Ach.) Grube</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Bäl-Gane, Gtl</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>719350</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6395059</v>
+      </c>
+      <c r="S99" t="n">
+        <v>25</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Bäl</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2018-09-26</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AL99" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74112681</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>74112682</v>
+      </c>
+      <c r="B100" t="n">
+        <v>75312</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>6000146</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Coniocarpon fallax</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Ach.) Grube</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Bäl-Gane, Gtl</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>719356</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6395063</v>
+      </c>
+      <c r="S100" t="n">
+        <v>25</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Bäl</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2018-09-26</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AL100" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74112682</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>74112683</v>
+      </c>
+      <c r="B101" t="n">
+        <v>75312</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>6000146</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Coniocarpon fallax</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Ach.) Grube</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Bäl-Gane, Gtl</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>719361</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6395058</v>
+      </c>
+      <c r="S101" t="n">
+        <v>25</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Bäl</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2018-09-26</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AL101" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74112683</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>74112684</v>
+      </c>
+      <c r="B102" t="n">
+        <v>75312</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>6000146</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Coniocarpon fallax</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Ach.) Grube</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Bäl-Gane, Gtl</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>719363</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6395058</v>
+      </c>
+      <c r="S102" t="n">
+        <v>25</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Bäl</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2018-09-26</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AL102" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74112684</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>74112686</v>
+      </c>
+      <c r="B103" t="n">
+        <v>75312</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>6000146</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Coniocarpon fallax</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Ach.) Grube</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Bäl-Gane, Gtl</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>719362</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6395060</v>
+      </c>
+      <c r="S103" t="n">
+        <v>25</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Bäl</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2018-09-26</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AL103" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74112686</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>74112687</v>
+      </c>
+      <c r="B104" t="n">
+        <v>75312</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>6000146</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Coniocarpon fallax</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Ach.) Grube</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Bäl-Gane, Gtl</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>719362</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6395063</v>
+      </c>
+      <c r="S104" t="n">
+        <v>25</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Bäl</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2018-09-26</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AL104" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74112687</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>74112688</v>
+      </c>
+      <c r="B105" t="n">
+        <v>75312</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>6000146</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Coniocarpon fallax</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Ach.) Grube</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Bäl-Gane, Gtl</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>719360</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6395065</v>
+      </c>
+      <c r="S105" t="n">
+        <v>25</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Bäl</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2018-09-26</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AL105" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74112688</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>74112689</v>
+      </c>
+      <c r="B106" t="n">
+        <v>75312</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>6000146</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Coniocarpon fallax</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Ach.) Grube</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Bäl-Gane, Gtl</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>719357</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6395067</v>
+      </c>
+      <c r="S106" t="n">
+        <v>25</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Bäl</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2018-09-26</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AL106" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74112689</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>74112691</v>
+      </c>
+      <c r="B107" t="n">
+        <v>75312</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>6000146</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Coniocarpon fallax</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Ach.) Grube</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Bäl-Gane, Gtl</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>719357</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6395061</v>
+      </c>
+      <c r="S107" t="n">
+        <v>25</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Bäl</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2018-09-26</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AL107" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74112691</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>74112639</v>
+      </c>
+      <c r="B108" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Bäl-Gane, Gtl</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>719439</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6395001</v>
+      </c>
+      <c r="S108" t="n">
+        <v>25</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Bäl</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2018-09-26</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74112639</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>112363481</v>
+      </c>
+      <c r="B109" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Säggeby Tjaut, Gtl</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>719399</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6395044</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Bäl</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/112363481</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>137124387</v>
+      </c>
+      <c r="B110" t="n">
+        <v>87529</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Bäl, Gtl</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>719352</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6394998</v>
+      </c>
+      <c r="S110" t="n">
+        <v>5</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Bäl</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137124387</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>137124388</v>
+      </c>
+      <c r="B111" t="n">
+        <v>87529</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Bäl, Gtl</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>719301</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6394905</v>
+      </c>
+      <c r="S111" t="n">
+        <v>5</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Bäl</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137124388</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>137124391</v>
+      </c>
+      <c r="B112" t="n">
+        <v>87529</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Bäl, Gtl</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>719418</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6394823</v>
+      </c>
+      <c r="S112" t="n">
+        <v>5</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Bäl</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137124391</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>137124392</v>
+      </c>
+      <c r="B113" t="n">
+        <v>87529</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Bäl, Gtl</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>719482</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6394901</v>
+      </c>
+      <c r="S113" t="n">
+        <v>5</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Bäl</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137124392</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>137124393</v>
+      </c>
+      <c r="B114" t="n">
+        <v>87529</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Bäl, Gtl</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>719609</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6395014</v>
+      </c>
+      <c r="S114" t="n">
+        <v>5</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Bäl</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137124393</t>
         </is>
       </c>
     </row>
@@ -11670,6 +13574,23 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27759-2026 artfynd.xlsx
+++ b/artfynd/A 27759-2026 artfynd.xlsx
@@ -1920,7 +1920,7 @@
         <v>137124402</v>
       </c>
       <c r="B13" t="n">
-        <v>87492</v>
+        <v>87498</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>137124403</v>
       </c>
       <c r="B14" t="n">
-        <v>87492</v>
+        <v>87498</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>137124405</v>
       </c>
       <c r="B15" t="n">
-        <v>87492</v>
+        <v>87498</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>137124410</v>
       </c>
       <c r="B16" t="n">
-        <v>87492</v>
+        <v>87498</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>137124411</v>
       </c>
       <c r="B17" t="n">
-        <v>87492</v>
+        <v>87498</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>137124389</v>
       </c>
       <c r="B18" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>137124397</v>
       </c>
       <c r="B19" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>137124390</v>
       </c>
       <c r="B21" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -8498,7 +8498,7 @@
         <v>137124398</v>
       </c>
       <c r="B71" t="n">
-        <v>102488</v>
+        <v>102494</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>137124401</v>
       </c>
       <c r="B90" t="n">
-        <v>87445</v>
+        <v>87451</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         <v>137124404</v>
       </c>
       <c r="B91" t="n">
-        <v>87445</v>
+        <v>87451</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>137124387</v>
       </c>
       <c r="B110" t="n">
-        <v>87529</v>
+        <v>87535</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>137124388</v>
       </c>
       <c r="B111" t="n">
-        <v>87529</v>
+        <v>87535</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         <v>137124391</v>
       </c>
       <c r="B112" t="n">
-        <v>87529</v>
+        <v>87535</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>137124392</v>
       </c>
       <c r="B113" t="n">
-        <v>87529</v>
+        <v>87535</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13369,7 +13369,7 @@
         <v>137124393</v>
       </c>
       <c r="B114" t="n">
-        <v>87529</v>
+        <v>87535</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>

--- a/artfynd/A 27759-2026 artfynd.xlsx
+++ b/artfynd/A 27759-2026 artfynd.xlsx
@@ -1920,7 +1920,7 @@
         <v>137124402</v>
       </c>
       <c r="B13" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>137124403</v>
       </c>
       <c r="B14" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>137124405</v>
       </c>
       <c r="B15" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>137124410</v>
       </c>
       <c r="B16" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>137124411</v>
       </c>
       <c r="B17" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>137124389</v>
       </c>
       <c r="B18" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>137124397</v>
       </c>
       <c r="B19" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>137124390</v>
       </c>
       <c r="B21" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -8498,7 +8498,7 @@
         <v>137124398</v>
       </c>
       <c r="B71" t="n">
-        <v>102494</v>
+        <v>102498</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>137124401</v>
       </c>
       <c r="B90" t="n">
-        <v>87451</v>
+        <v>87455</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         <v>137124404</v>
       </c>
       <c r="B91" t="n">
-        <v>87451</v>
+        <v>87455</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>137124387</v>
       </c>
       <c r="B110" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>137124388</v>
       </c>
       <c r="B111" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         <v>137124391</v>
       </c>
       <c r="B112" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>137124392</v>
       </c>
       <c r="B113" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13369,7 +13369,7 @@
         <v>137124393</v>
       </c>
       <c r="B114" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>

--- a/artfynd/A 27759-2026 artfynd.xlsx
+++ b/artfynd/A 27759-2026 artfynd.xlsx
@@ -8498,7 +8498,7 @@
         <v>137124398</v>
       </c>
       <c r="B71" t="n">
-        <v>102498</v>
+        <v>102500</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 27759-2026 artfynd.xlsx
+++ b/artfynd/A 27759-2026 artfynd.xlsx
@@ -1920,7 +1920,7 @@
         <v>137124402</v>
       </c>
       <c r="B13" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>137124403</v>
       </c>
       <c r="B14" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>137124405</v>
       </c>
       <c r="B15" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>137124410</v>
       </c>
       <c r="B16" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>137124411</v>
       </c>
       <c r="B17" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>137124389</v>
       </c>
       <c r="B18" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>137124397</v>
       </c>
       <c r="B19" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>137124390</v>
       </c>
       <c r="B21" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -8498,7 +8498,7 @@
         <v>137124398</v>
       </c>
       <c r="B71" t="n">
-        <v>102500</v>
+        <v>102502</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>137124401</v>
       </c>
       <c r="B90" t="n">
-        <v>87455</v>
+        <v>87457</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         <v>137124404</v>
       </c>
       <c r="B91" t="n">
-        <v>87455</v>
+        <v>87457</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>137124387</v>
       </c>
       <c r="B110" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>137124388</v>
       </c>
       <c r="B111" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         <v>137124391</v>
       </c>
       <c r="B112" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>137124392</v>
       </c>
       <c r="B113" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13369,7 +13369,7 @@
         <v>137124393</v>
       </c>
       <c r="B114" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>

--- a/artfynd/A 27759-2026 artfynd.xlsx
+++ b/artfynd/A 27759-2026 artfynd.xlsx
@@ -1920,7 +1920,7 @@
         <v>137124402</v>
       </c>
       <c r="B13" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>137124403</v>
       </c>
       <c r="B14" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>137124405</v>
       </c>
       <c r="B15" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>137124410</v>
       </c>
       <c r="B16" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>137124411</v>
       </c>
       <c r="B17" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>137124389</v>
       </c>
       <c r="B18" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>137124397</v>
       </c>
       <c r="B19" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>137124390</v>
       </c>
       <c r="B21" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>137124399</v>
       </c>
       <c r="B22" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -8498,7 +8498,7 @@
         <v>137124398</v>
       </c>
       <c r="B71" t="n">
-        <v>102502</v>
+        <v>102515</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>137124401</v>
       </c>
       <c r="B90" t="n">
-        <v>87457</v>
+        <v>87470</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         <v>137124404</v>
       </c>
       <c r="B91" t="n">
-        <v>87457</v>
+        <v>87470</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>137124387</v>
       </c>
       <c r="B110" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>137124388</v>
       </c>
       <c r="B111" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         <v>137124391</v>
       </c>
       <c r="B112" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>137124392</v>
       </c>
       <c r="B113" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13369,7 +13369,7 @@
         <v>137124393</v>
       </c>
       <c r="B114" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>

--- a/artfynd/A 27759-2026 artfynd.xlsx
+++ b/artfynd/A 27759-2026 artfynd.xlsx
@@ -1920,7 +1920,7 @@
         <v>137124402</v>
       </c>
       <c r="B13" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>137124403</v>
       </c>
       <c r="B14" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>137124405</v>
       </c>
       <c r="B15" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>137124410</v>
       </c>
       <c r="B16" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>137124411</v>
       </c>
       <c r="B17" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>137124389</v>
       </c>
       <c r="B18" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>137124397</v>
       </c>
       <c r="B19" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>137124390</v>
       </c>
       <c r="B21" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>137124399</v>
       </c>
       <c r="B22" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -8498,7 +8498,7 @@
         <v>137124398</v>
       </c>
       <c r="B71" t="n">
-        <v>102515</v>
+        <v>102517</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>137124401</v>
       </c>
       <c r="B90" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         <v>137124404</v>
       </c>
       <c r="B91" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>137124387</v>
       </c>
       <c r="B110" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>137124388</v>
       </c>
       <c r="B111" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         <v>137124391</v>
       </c>
       <c r="B112" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>137124392</v>
       </c>
       <c r="B113" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13369,7 +13369,7 @@
         <v>137124393</v>
       </c>
       <c r="B114" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>

--- a/artfynd/A 27759-2026 artfynd.xlsx
+++ b/artfynd/A 27759-2026 artfynd.xlsx
@@ -1920,7 +1920,7 @@
         <v>137124402</v>
       </c>
       <c r="B13" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>137124403</v>
       </c>
       <c r="B14" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>137124405</v>
       </c>
       <c r="B15" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>137124410</v>
       </c>
       <c r="B16" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>137124411</v>
       </c>
       <c r="B17" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>137124389</v>
       </c>
       <c r="B18" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>137124397</v>
       </c>
       <c r="B19" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>137124390</v>
       </c>
       <c r="B21" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -8498,7 +8498,7 @@
         <v>137124398</v>
       </c>
       <c r="B71" t="n">
-        <v>102517</v>
+        <v>102520</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>137124401</v>
       </c>
       <c r="B90" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         <v>137124404</v>
       </c>
       <c r="B91" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>137124387</v>
       </c>
       <c r="B110" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>137124388</v>
       </c>
       <c r="B111" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         <v>137124391</v>
       </c>
       <c r="B112" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>137124392</v>
       </c>
       <c r="B113" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13369,7 +13369,7 @@
         <v>137124393</v>
       </c>
       <c r="B114" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>

--- a/artfynd/A 27759-2026 artfynd.xlsx
+++ b/artfynd/A 27759-2026 artfynd.xlsx
@@ -1920,7 +1920,7 @@
         <v>137124402</v>
       </c>
       <c r="B13" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>137124403</v>
       </c>
       <c r="B14" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>137124405</v>
       </c>
       <c r="B15" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>137124410</v>
       </c>
       <c r="B16" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>137124411</v>
       </c>
       <c r="B17" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>137124389</v>
       </c>
       <c r="B18" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>137124397</v>
       </c>
       <c r="B19" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>137124390</v>
       </c>
       <c r="B21" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>137124399</v>
       </c>
       <c r="B22" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -8498,7 +8498,7 @@
         <v>137124398</v>
       </c>
       <c r="B71" t="n">
-        <v>102520</v>
+        <v>102535</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>137124401</v>
       </c>
       <c r="B90" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         <v>137124404</v>
       </c>
       <c r="B91" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>137124387</v>
       </c>
       <c r="B110" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>137124388</v>
       </c>
       <c r="B111" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         <v>137124391</v>
       </c>
       <c r="B112" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>137124392</v>
       </c>
       <c r="B113" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13369,7 +13369,7 @@
         <v>137124393</v>
       </c>
       <c r="B114" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>

--- a/artfynd/A 27759-2026 artfynd.xlsx
+++ b/artfynd/A 27759-2026 artfynd.xlsx
@@ -1920,7 +1920,7 @@
         <v>137124402</v>
       </c>
       <c r="B13" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>137124403</v>
       </c>
       <c r="B14" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>137124405</v>
       </c>
       <c r="B15" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>137124410</v>
       </c>
       <c r="B16" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>137124411</v>
       </c>
       <c r="B17" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>137124389</v>
       </c>
       <c r="B18" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>137124397</v>
       </c>
       <c r="B19" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>137124390</v>
       </c>
       <c r="B21" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -8498,7 +8498,7 @@
         <v>137124398</v>
       </c>
       <c r="B71" t="n">
-        <v>102535</v>
+        <v>102536</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>137124401</v>
       </c>
       <c r="B90" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         <v>137124404</v>
       </c>
       <c r="B91" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>137124387</v>
       </c>
       <c r="B110" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>137124388</v>
       </c>
       <c r="B111" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         <v>137124391</v>
       </c>
       <c r="B112" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>137124392</v>
       </c>
       <c r="B113" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13369,7 +13369,7 @@
         <v>137124393</v>
       </c>
       <c r="B114" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>

--- a/artfynd/A 27759-2026 artfynd.xlsx
+++ b/artfynd/A 27759-2026 artfynd.xlsx
@@ -1920,7 +1920,7 @@
         <v>137124402</v>
       </c>
       <c r="B13" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>137124403</v>
       </c>
       <c r="B14" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>137124405</v>
       </c>
       <c r="B15" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>137124410</v>
       </c>
       <c r="B16" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>137124411</v>
       </c>
       <c r="B17" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>137124389</v>
       </c>
       <c r="B18" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>137124397</v>
       </c>
       <c r="B19" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>137124390</v>
       </c>
       <c r="B21" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>137124399</v>
       </c>
       <c r="B22" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -8498,7 +8498,7 @@
         <v>137124398</v>
       </c>
       <c r="B71" t="n">
-        <v>102536</v>
+        <v>102541</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>137124401</v>
       </c>
       <c r="B90" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         <v>137124404</v>
       </c>
       <c r="B91" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>137124387</v>
       </c>
       <c r="B110" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>137124388</v>
       </c>
       <c r="B111" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         <v>137124391</v>
       </c>
       <c r="B112" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>137124392</v>
       </c>
       <c r="B113" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13369,7 +13369,7 @@
         <v>137124393</v>
       </c>
       <c r="B114" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>

--- a/artfynd/A 27759-2026 artfynd.xlsx
+++ b/artfynd/A 27759-2026 artfynd.xlsx
@@ -2480,7 +2480,7 @@
         <v>137124389</v>
       </c>
       <c r="B18" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>137124397</v>
       </c>
       <c r="B19" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>137124390</v>
       </c>
       <c r="B21" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -8498,7 +8498,7 @@
         <v>137124398</v>
       </c>
       <c r="B71" t="n">
-        <v>102541</v>
+        <v>102544</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 27759-2026 artfynd.xlsx
+++ b/artfynd/A 27759-2026 artfynd.xlsx
@@ -1920,7 +1920,7 @@
         <v>137124402</v>
       </c>
       <c r="B13" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>137124403</v>
       </c>
       <c r="B14" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>137124405</v>
       </c>
       <c r="B15" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>137124410</v>
       </c>
       <c r="B16" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>137124411</v>
       </c>
       <c r="B17" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>137124389</v>
       </c>
       <c r="B18" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>137124397</v>
       </c>
       <c r="B19" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>137124390</v>
       </c>
       <c r="B21" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>137124399</v>
       </c>
       <c r="B22" t="n">
-        <v>75594</v>
+        <v>75599</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -8498,7 +8498,7 @@
         <v>137124398</v>
       </c>
       <c r="B71" t="n">
-        <v>102544</v>
+        <v>102550</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>137124401</v>
       </c>
       <c r="B90" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         <v>137124404</v>
       </c>
       <c r="B91" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>137124387</v>
       </c>
       <c r="B110" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>137124388</v>
       </c>
       <c r="B111" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         <v>137124391</v>
       </c>
       <c r="B112" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>137124392</v>
       </c>
       <c r="B113" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13369,7 +13369,7 @@
         <v>137124393</v>
       </c>
       <c r="B114" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>

--- a/artfynd/A 27759-2026 artfynd.xlsx
+++ b/artfynd/A 27759-2026 artfynd.xlsx
@@ -1920,7 +1920,7 @@
         <v>137124402</v>
       </c>
       <c r="B13" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>137124403</v>
       </c>
       <c r="B14" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>137124405</v>
       </c>
       <c r="B15" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>137124410</v>
       </c>
       <c r="B16" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>137124411</v>
       </c>
       <c r="B17" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>137124389</v>
       </c>
       <c r="B18" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>137124397</v>
       </c>
       <c r="B19" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>137124390</v>
       </c>
       <c r="B21" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>137124399</v>
       </c>
       <c r="B22" t="n">
-        <v>75599</v>
+        <v>75610</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -8498,7 +8498,7 @@
         <v>137124398</v>
       </c>
       <c r="B71" t="n">
-        <v>102550</v>
+        <v>102562</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>137124401</v>
       </c>
       <c r="B90" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         <v>137124404</v>
       </c>
       <c r="B91" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>137124387</v>
       </c>
       <c r="B110" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>137124388</v>
       </c>
       <c r="B111" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         <v>137124391</v>
       </c>
       <c r="B112" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>137124392</v>
       </c>
       <c r="B113" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13369,7 +13369,7 @@
         <v>137124393</v>
       </c>
       <c r="B114" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>

--- a/artfynd/A 27759-2026 artfynd.xlsx
+++ b/artfynd/A 27759-2026 artfynd.xlsx
@@ -1920,7 +1920,7 @@
         <v>137124402</v>
       </c>
       <c r="B13" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>137124403</v>
       </c>
       <c r="B14" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>137124405</v>
       </c>
       <c r="B15" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>137124410</v>
       </c>
       <c r="B16" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>137124411</v>
       </c>
       <c r="B17" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>137124389</v>
       </c>
       <c r="B18" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>137124397</v>
       </c>
       <c r="B19" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>137124390</v>
       </c>
       <c r="B21" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -8498,7 +8498,7 @@
         <v>137124398</v>
       </c>
       <c r="B71" t="n">
-        <v>102562</v>
+        <v>102563</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>137124401</v>
       </c>
       <c r="B90" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         <v>137124404</v>
       </c>
       <c r="B91" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>137124387</v>
       </c>
       <c r="B110" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>137124388</v>
       </c>
       <c r="B111" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         <v>137124391</v>
       </c>
       <c r="B112" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>137124392</v>
       </c>
       <c r="B113" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13369,7 +13369,7 @@
         <v>137124393</v>
       </c>
       <c r="B114" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>

--- a/artfynd/A 27759-2026 artfynd.xlsx
+++ b/artfynd/A 27759-2026 artfynd.xlsx
@@ -1920,7 +1920,7 @@
         <v>137124402</v>
       </c>
       <c r="B13" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>137124403</v>
       </c>
       <c r="B14" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>137124405</v>
       </c>
       <c r="B15" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>137124410</v>
       </c>
       <c r="B16" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>137124411</v>
       </c>
       <c r="B17" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>137124389</v>
       </c>
       <c r="B18" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>137124397</v>
       </c>
       <c r="B19" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>137124390</v>
       </c>
       <c r="B21" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -8498,7 +8498,7 @@
         <v>137124398</v>
       </c>
       <c r="B71" t="n">
-        <v>102563</v>
+        <v>102566</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>137124401</v>
       </c>
       <c r="B90" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         <v>137124404</v>
       </c>
       <c r="B91" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>137124387</v>
       </c>
       <c r="B110" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>137124388</v>
       </c>
       <c r="B111" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         <v>137124391</v>
       </c>
       <c r="B112" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>137124392</v>
       </c>
       <c r="B113" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13369,7 +13369,7 @@
         <v>137124393</v>
       </c>
       <c r="B114" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>

--- a/artfynd/A 27759-2026 artfynd.xlsx
+++ b/artfynd/A 27759-2026 artfynd.xlsx
@@ -1920,7 +1920,7 @@
         <v>137124402</v>
       </c>
       <c r="B13" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>137124403</v>
       </c>
       <c r="B14" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>137124405</v>
       </c>
       <c r="B15" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>137124410</v>
       </c>
       <c r="B16" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>137124411</v>
       </c>
       <c r="B17" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>137124389</v>
       </c>
       <c r="B18" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>137124397</v>
       </c>
       <c r="B19" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>137124390</v>
       </c>
       <c r="B21" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>137124399</v>
       </c>
       <c r="B22" t="n">
-        <v>75610</v>
+        <v>75614</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -8498,7 +8498,7 @@
         <v>137124398</v>
       </c>
       <c r="B71" t="n">
-        <v>102566</v>
+        <v>102570</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>137124401</v>
       </c>
       <c r="B90" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         <v>137124404</v>
       </c>
       <c r="B91" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>137124387</v>
       </c>
       <c r="B110" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>137124388</v>
       </c>
       <c r="B111" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         <v>137124391</v>
       </c>
       <c r="B112" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>137124392</v>
       </c>
       <c r="B113" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13369,7 +13369,7 @@
         <v>137124393</v>
       </c>
       <c r="B114" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
